--- a/Termin 16/overdue_users.xlsx
+++ b/Termin 16/overdue_users.xlsx
@@ -417,46 +417,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>firstname</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>firstname</t>
+          <t>lastname</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>lastname</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>total_rentals</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>total_rentals</t>
+          <t>rental_book_id</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>rental_book_id</t>
+          <t>rental_date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>rental_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>overdue_days</t>
         </is>
@@ -464,4100 +464,3751 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B2" t="n">
         <v>69</v>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Benton</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Benton</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>+1 (355) 857-4411</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
       <c r="F2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G2" t="n">
         <v>25</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103</v>
-      </c>
-      <c r="B3" t="n">
         <v>104</v>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Joshua</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Lopez</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lopez</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>+1 (309) 355-5002</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
       <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
         <v>430</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B4" t="n">
         <v>37</v>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Shane</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shane</t>
+          <t>Conway</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Conway</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>+1 (303) 652-8480</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
       <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
         <v>50</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="I4" t="n">
+      <c r="H4" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>269</v>
-      </c>
-      <c r="B5" t="n">
         <v>270</v>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wilson</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>+1 (509) 466-9305</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
       <c r="F5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" t="n">
         <v>331</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202</v>
-      </c>
-      <c r="B6" t="n">
         <v>203</v>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cindy</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>French</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>+1 (823) 238-5685</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
       <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
         <v>440</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="I6" t="n">
+      <c r="H6" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107</v>
-      </c>
-      <c r="B7" t="n">
         <v>108</v>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Watkins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Watkins</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>+1 (442) 909-5180</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
         <v>478</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="I7" t="n">
+      <c r="H7" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119</v>
-      </c>
-      <c r="B8" t="n">
         <v>120</v>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lucas</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>+1 (927) 722-9934</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
       <c r="F8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="n">
         <v>26</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="I8" t="n">
+      <c r="H8" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>196</v>
-      </c>
-      <c r="B9" t="n">
         <v>197</v>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>+1 (474) 203-2887</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>18</v>
+      </c>
       <c r="F9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G9" t="n">
         <v>481</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="I9" t="n">
+      <c r="H9" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>238</v>
-      </c>
-      <c r="B10" t="n">
         <v>239</v>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Watson</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>+1 (864) 794-3911</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
         <v>89</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="I10" t="n">
+      <c r="H10" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>50</v>
-      </c>
-      <c r="B11" t="n">
         <v>51</v>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jeffrey</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jeffrey</t>
+          <t>Mckenzie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mckenzie</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>+1 (316) 535-1207</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
       <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
         <v>320</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>46007</v>
       </c>
-      <c r="I11" t="n">
+      <c r="H11" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94</v>
-      </c>
-      <c r="B12" t="n">
         <v>95</v>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Nunez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nunez</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>+1 (887) 567-9795</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
       <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
         <v>113</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="G12" s="1" t="n">
         <v>46007</v>
       </c>
-      <c r="I12" t="n">
+      <c r="H12" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120</v>
-      </c>
-      <c r="B13" t="n">
         <v>121</v>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jody</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jody</t>
+          <t>Reeves</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Reeves</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>+1 (308) 221-5292</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
       <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
         <v>451</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="I13" t="n">
+      <c r="H13" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123</v>
-      </c>
-      <c r="B14" t="n">
         <v>124</v>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vanessa</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Decker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Decker</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>+1 (611) 544-3273</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
       <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
         <v>238</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="I14" t="n">
+      <c r="H14" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>146</v>
-      </c>
-      <c r="B15" t="n">
         <v>147</v>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Shirley</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Alexander</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>+1 (650) 668-3907</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
       <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
         <v>32</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="I15" t="n">
+      <c r="H15" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>295</v>
-      </c>
-      <c r="B16" t="n">
         <v>296</v>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Arthur</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Schmitt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Schmitt</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>+1 (745) 673-5401</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
         <v>206</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="G16" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="I16" t="n">
+      <c r="H16" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>217</v>
-      </c>
-      <c r="B17" t="n">
         <v>218</v>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Johnston</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>+1 (777) 831-4095</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>14</v>
+      </c>
       <c r="F17" t="n">
-        <v>14</v>
-      </c>
-      <c r="G17" t="n">
         <v>165</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="G17" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="I17" t="n">
+      <c r="H17" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>292</v>
-      </c>
-      <c r="B18" t="n">
         <v>293</v>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Keith</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Keith</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Moore</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
           <t>+1 (454) 584-6646</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
       <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="n">
         <v>167</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="G18" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="I18" t="n">
+      <c r="H18" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>299</v>
-      </c>
-      <c r="B19" t="n">
         <v>300</v>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Salazar</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Salazar</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
           <t>+1 (827) 903-8398</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>13</v>
+      </c>
       <c r="F19" t="n">
-        <v>13</v>
-      </c>
-      <c r="G19" t="n">
         <v>205</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="G19" s="1" t="n">
         <v>46009</v>
       </c>
-      <c r="I19" t="n">
+      <c r="H19" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>210</v>
-      </c>
-      <c r="B20" t="n">
         <v>211</v>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jill</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jill</t>
+          <t>Sparks</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sparks</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
           <t>+1 (482) 850-7972</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
       <c r="F20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" t="n">
         <v>311</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="G20" s="1" t="n">
         <v>46009</v>
       </c>
-      <c r="I20" t="n">
+      <c r="H20" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>190</v>
-      </c>
-      <c r="B21" t="n">
         <v>191</v>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Renee</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Renee</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Davis</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
           <t>+1 (810) 448-9233</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>16</v>
+      </c>
       <c r="F21" t="n">
-        <v>16</v>
-      </c>
-      <c r="G21" t="n">
         <v>148</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="G21" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="I21" t="n">
+      <c r="H21" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>241</v>
-      </c>
-      <c r="B22" t="n">
         <v>242</v>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
           <t>+1 (930) 910-1227</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>11</v>
+      </c>
       <c r="F22" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" t="n">
         <v>239</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="G22" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="I22" t="n">
+      <c r="H22" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>293</v>
-      </c>
-      <c r="B23" t="n">
         <v>294</v>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shawn</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shawn</t>
+          <t>Flores</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Flores</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
           <t>+1 (897) 587-6227</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
       <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" t="n">
         <v>174</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="I23" t="n">
+      <c r="H23" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>224</v>
-      </c>
-      <c r="B24" t="n">
         <v>225</v>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ricky</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ricky</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Patterson</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>+1 (370) 312-4026</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
       <c r="F24" t="n">
-        <v>12</v>
-      </c>
-      <c r="G24" t="n">
         <v>428</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="G24" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="I24" t="n">
+      <c r="H24" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>243</v>
-      </c>
-      <c r="B25" t="n">
         <v>244</v>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Marquez</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Marquez</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
           <t>+1 (636) 487-4678</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
       <c r="F25" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" t="n">
         <v>36</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="G25" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="I25" t="n">
+      <c r="H25" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mcknight</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>+1 (808) 753-3917</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>15</v>
       </c>
-      <c r="B26" t="n">
-        <v>16</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Mcknight</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>+1 (808) 753-3917</t>
-        </is>
-      </c>
       <c r="F26" t="n">
-        <v>15</v>
-      </c>
-      <c r="G26" t="n">
         <v>454</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="G26" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="I26" t="n">
+      <c r="H26" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>250</v>
-      </c>
-      <c r="B27" t="n">
         <v>251</v>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Poole</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
           <t>+1 (881) 914-8486</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>14</v>
+      </c>
       <c r="F27" t="n">
-        <v>14</v>
-      </c>
-      <c r="G27" t="n">
         <v>262</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="G27" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="I27" t="n">
+      <c r="H27" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>65</v>
-      </c>
-      <c r="B28" t="n">
         <v>66</v>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Harding</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Harding</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
           <t>+1 (849) 655-4039</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
       <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
         <v>141</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="G28" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="I28" t="n">
+      <c r="H28" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118</v>
-      </c>
-      <c r="B29" t="n">
         <v>119</v>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Munoz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Munoz</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
           <t>+1 (322) 837-8532</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
       <c r="F29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" t="n">
         <v>175</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="G29" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="I29" t="n">
+      <c r="H29" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>265</v>
-      </c>
-      <c r="B30" t="n">
         <v>266</v>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Blair</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
           <t>+1 (730) 934-5644</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
       <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
         <v>237</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="G30" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="I30" t="n">
+      <c r="H30" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>203</v>
-      </c>
-      <c r="B31" t="n">
         <v>204</v>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Savage</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
           <t>+1 (747) 914-4625</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>17</v>
+      </c>
       <c r="F31" t="n">
-        <v>17</v>
-      </c>
-      <c r="G31" t="n">
         <v>158</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="G31" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="I31" t="n">
+      <c r="H31" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>72</v>
-      </c>
-      <c r="B32" t="n">
         <v>73</v>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Kline</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kline</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
           <t>+1 (208) 874-9143</t>
         </is>
       </c>
+      <c r="E32" t="n">
+        <v>17</v>
+      </c>
       <c r="F32" t="n">
-        <v>17</v>
-      </c>
-      <c r="G32" t="n">
         <v>342</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="G32" s="1" t="n">
         <v>46014</v>
       </c>
-      <c r="I32" t="n">
+      <c r="H32" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>21</v>
-      </c>
-      <c r="B33" t="n">
         <v>22</v>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Carr</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
           <t>+1 (348) 818-7151</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
       <c r="F33" t="n">
-        <v>8</v>
-      </c>
-      <c r="G33" t="n">
         <v>360</v>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="G33" s="1" t="n">
         <v>46014</v>
       </c>
-      <c r="I33" t="n">
+      <c r="H33" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>189</v>
-      </c>
-      <c r="B34" t="n">
         <v>190</v>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
           <t>+1 (757) 545-3104</t>
         </is>
       </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
       <c r="F34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G34" t="n">
         <v>16</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="G34" s="1" t="n">
         <v>46014</v>
       </c>
-      <c r="I34" t="n">
+      <c r="H34" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>140</v>
-      </c>
-      <c r="B35" t="n">
         <v>141</v>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
           <t>+1 (800) 558-6873</t>
         </is>
       </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
       <c r="F35" t="n">
-        <v>6</v>
-      </c>
-      <c r="G35" t="n">
         <v>299</v>
       </c>
-      <c r="H35" s="1" t="n">
+      <c r="G35" s="1" t="n">
         <v>46014</v>
       </c>
-      <c r="I35" t="n">
+      <c r="H35" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>78</v>
-      </c>
-      <c r="B36" t="n">
         <v>79</v>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Hawkins</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hawkins</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
           <t>+1 (860) 982-9890</t>
         </is>
       </c>
+      <c r="E36" t="n">
+        <v>8</v>
+      </c>
       <c r="F36" t="n">
-        <v>8</v>
-      </c>
-      <c r="G36" t="n">
         <v>452</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="G36" s="1" t="n">
         <v>46014</v>
       </c>
-      <c r="I36" t="n">
+      <c r="H36" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>43</v>
-      </c>
-      <c r="B37" t="n">
         <v>44</v>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wilson</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
           <t>+1 (811) 749-2570</t>
         </is>
       </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
       <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="n">
         <v>333</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="G37" s="1" t="n">
         <v>46015</v>
       </c>
-      <c r="I37" t="n">
+      <c r="H37" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128</v>
-      </c>
-      <c r="B38" t="n">
         <v>129</v>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Brandi</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brandi</t>
+          <t>Little</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Little</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
           <t>+1 (490) 224-7944</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
       <c r="F38" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" t="n">
         <v>309</v>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="G38" s="1" t="n">
         <v>46015</v>
       </c>
-      <c r="I38" t="n">
+      <c r="H38" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135</v>
-      </c>
-      <c r="B39" t="n">
         <v>136</v>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Riley</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
           <t>+1 (374) 793-4020</t>
         </is>
       </c>
+      <c r="E39" t="n">
+        <v>18</v>
+      </c>
       <c r="F39" t="n">
-        <v>18</v>
-      </c>
-      <c r="G39" t="n">
         <v>166</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="G39" s="1" t="n">
         <v>46015</v>
       </c>
-      <c r="I39" t="n">
+      <c r="H39" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>81</v>
-      </c>
-      <c r="B40" t="n">
         <v>82</v>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Fritz</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fritz</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
           <t>+1 (539) 495-3830</t>
         </is>
       </c>
+      <c r="E40" t="n">
+        <v>15</v>
+      </c>
       <c r="F40" t="n">
-        <v>15</v>
-      </c>
-      <c r="G40" t="n">
         <v>111</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="G40" s="1" t="n">
         <v>46016</v>
       </c>
-      <c r="I40" t="n">
+      <c r="H40" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>139</v>
-      </c>
-      <c r="B41" t="n">
         <v>140</v>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Steven</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
           <t>+1 (809) 252-8895</t>
         </is>
       </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
       <c r="F41" t="n">
-        <v>8</v>
-      </c>
-      <c r="G41" t="n">
         <v>413</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="G41" s="1" t="n">
         <v>46016</v>
       </c>
-      <c r="I41" t="n">
+      <c r="H41" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>49</v>
-      </c>
-      <c r="B42" t="n">
         <v>50</v>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wright</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
           <t>+1 (206) 530-1402</t>
         </is>
       </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
       <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
         <v>441</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="G42" s="1" t="n">
         <v>46016</v>
       </c>
-      <c r="I42" t="n">
+      <c r="H42" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
-      </c>
-      <c r="B43" t="n">
         <v>17</v>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Weaver</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Weaver</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
           <t>+1 (453) 453-9474</t>
         </is>
       </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
       <c r="F43" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" t="n">
         <v>104</v>
       </c>
-      <c r="H43" s="1" t="n">
+      <c r="G43" s="1" t="n">
         <v>46017</v>
       </c>
-      <c r="I43" t="n">
+      <c r="H43" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>95</v>
-      </c>
-      <c r="B44" t="n">
         <v>96</v>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
           <t>+1 (403) 364-8754</t>
         </is>
       </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
       <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="n">
         <v>272</v>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="G44" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="I44" t="n">
+      <c r="H44" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Phillips</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>+1 (701) 203-1607</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Timothy</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Phillips</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>+1 (701) 203-1607</t>
-        </is>
-      </c>
       <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
         <v>269</v>
       </c>
-      <c r="H45" s="1" t="n">
+      <c r="G45" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="I45" t="n">
+      <c r="H45" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>172</v>
-      </c>
-      <c r="B46" t="n">
         <v>173</v>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bauer</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
           <t>+1 (749) 812-1792</t>
         </is>
       </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
       <c r="F46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" t="n">
         <v>225</v>
       </c>
-      <c r="H46" s="1" t="n">
+      <c r="G46" s="1" t="n">
         <v>46019</v>
       </c>
-      <c r="I46" t="n">
+      <c r="H46" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>281</v>
-      </c>
-      <c r="B47" t="n">
         <v>282</v>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rodney</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rodney</t>
+          <t>Hanson</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hanson</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
           <t>+1 (498) 254-6521</t>
         </is>
       </c>
+      <c r="E47" t="n">
+        <v>9</v>
+      </c>
       <c r="F47" t="n">
-        <v>9</v>
-      </c>
-      <c r="G47" t="n">
         <v>246</v>
       </c>
-      <c r="H47" s="1" t="n">
+      <c r="G47" s="1" t="n">
         <v>46019</v>
       </c>
-      <c r="I47" t="n">
+      <c r="H47" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>280</v>
-      </c>
-      <c r="B48" t="n">
         <v>281</v>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cunningham</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
           <t>+1 (657) 880-1561</t>
         </is>
       </c>
+      <c r="E48" t="n">
+        <v>17</v>
+      </c>
       <c r="F48" t="n">
-        <v>17</v>
-      </c>
-      <c r="G48" t="n">
         <v>181</v>
       </c>
-      <c r="H48" s="1" t="n">
+      <c r="G48" s="1" t="n">
         <v>46019</v>
       </c>
-      <c r="I48" t="n">
+      <c r="H48" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>188</v>
-      </c>
-      <c r="B49" t="n">
         <v>189</v>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Riggs</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Riggs</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
           <t>+1 (416) 692-4244</t>
         </is>
       </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
       <c r="F49" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" t="n">
         <v>92</v>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="G49" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="I49" t="n">
+      <c r="H49" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>194</v>
-      </c>
-      <c r="B50" t="n">
         <v>195</v>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Nicholson</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Nicholson</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
           <t>+1 (768) 952-6721</t>
         </is>
       </c>
+      <c r="E50" t="n">
+        <v>11</v>
+      </c>
       <c r="F50" t="n">
-        <v>11</v>
-      </c>
-      <c r="G50" t="n">
         <v>240</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="G50" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="I50" t="n">
+      <c r="H50" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>262</v>
-      </c>
-      <c r="B51" t="n">
         <v>263</v>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Terry</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
           <t>+1 (597) 703-4531</t>
         </is>
       </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
       <c r="F51" t="n">
-        <v>10</v>
-      </c>
-      <c r="G51" t="n">
         <v>204</v>
       </c>
-      <c r="H51" s="1" t="n">
+      <c r="G51" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="I51" t="n">
+      <c r="H51" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>19</v>
-      </c>
-      <c r="B52" t="n">
         <v>20</v>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
           <t>+1 (572) 328-6863</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
         <v>366</v>
       </c>
-      <c r="H52" s="1" t="n">
+      <c r="G52" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="I52" t="n">
+      <c r="H52" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>277</v>
-      </c>
-      <c r="B53" t="n">
         <v>278</v>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
           <t>+1 (438) 685-9857</t>
         </is>
       </c>
+      <c r="E53" t="n">
+        <v>12</v>
+      </c>
       <c r="F53" t="n">
-        <v>12</v>
-      </c>
-      <c r="G53" t="n">
         <v>66</v>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="G53" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="I53" t="n">
+      <c r="H53" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>27</v>
-      </c>
-      <c r="B54" t="n">
         <v>28</v>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Caitlyn</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Caitlyn</t>
+          <t>Payne</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Payne</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
           <t>+1 (611) 931-2818</t>
         </is>
       </c>
+      <c r="E54" t="n">
+        <v>16</v>
+      </c>
       <c r="F54" t="n">
-        <v>16</v>
-      </c>
-      <c r="G54" t="n">
         <v>282</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="G54" s="1" t="n">
         <v>46021</v>
       </c>
-      <c r="I54" t="n">
+      <c r="H54" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>76</v>
-      </c>
-      <c r="B55" t="n">
         <v>77</v>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alejandra</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nelson</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
           <t>+1 (279) 684-1585</t>
         </is>
       </c>
+      <c r="E55" t="n">
+        <v>8</v>
+      </c>
       <c r="F55" t="n">
-        <v>8</v>
-      </c>
-      <c r="G55" t="n">
         <v>51</v>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="G55" s="1" t="n">
         <v>46021</v>
       </c>
-      <c r="I55" t="n">
+      <c r="H55" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>288</v>
-      </c>
-      <c r="B56" t="n">
         <v>289</v>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Moore</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
           <t>+1 (355) 528-2408</t>
         </is>
       </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
       <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
         <v>285</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="G56" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="I56" t="n">
+      <c r="H56" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>144</v>
-      </c>
-      <c r="B57" t="n">
         <v>145</v>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Marshall</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
           <t>+1 (765) 911-9422</t>
         </is>
       </c>
+      <c r="E57" t="n">
+        <v>18</v>
+      </c>
       <c r="F57" t="n">
-        <v>18</v>
-      </c>
-      <c r="G57" t="n">
         <v>453</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="G57" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="I57" t="n">
+      <c r="H57" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>209</v>
-      </c>
-      <c r="B58" t="n">
         <v>210</v>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Sherry</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sherry</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
           <t>+1 (686) 448-4863</t>
         </is>
       </c>
+      <c r="E58" t="n">
+        <v>17</v>
+      </c>
       <c r="F58" t="n">
-        <v>17</v>
-      </c>
-      <c r="G58" t="n">
         <v>169</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>46023</v>
       </c>
-      <c r="I58" t="n">
+      <c r="H58" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>33</v>
-      </c>
-      <c r="B59" t="n">
         <v>34</v>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Williams</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
           <t>+1 (554) 351-9662</t>
         </is>
       </c>
+      <c r="E59" t="n">
+        <v>13</v>
+      </c>
       <c r="F59" t="n">
-        <v>13</v>
-      </c>
-      <c r="G59" t="n">
         <v>305</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>46024</v>
       </c>
-      <c r="I59" t="n">
+      <c r="H59" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>244</v>
-      </c>
-      <c r="B60" t="n">
         <v>245</v>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Autumn</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Autumn</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
           <t>+1 (723) 717-8362</t>
         </is>
       </c>
+      <c r="E60" t="n">
+        <v>13</v>
+      </c>
       <c r="F60" t="n">
-        <v>13</v>
-      </c>
-      <c r="G60" t="n">
         <v>306</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="G60" s="1" t="n">
         <v>46025</v>
       </c>
-      <c r="I60" t="n">
+      <c r="H60" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>290</v>
-      </c>
-      <c r="B61" t="n">
         <v>291</v>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Rojas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Rojas</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
           <t>+1 (754) 743-5880</t>
         </is>
       </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
       <c r="F61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" t="n">
         <v>391</v>
       </c>
-      <c r="H61" s="1" t="n">
+      <c r="G61" s="1" t="n">
         <v>46025</v>
       </c>
-      <c r="I61" t="n">
+      <c r="H61" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>257</v>
-      </c>
-      <c r="B62" t="n">
         <v>258</v>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jacqueline</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacqueline</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
           <t>+1 (297) 266-2843</t>
         </is>
       </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
       <c r="F62" t="n">
-        <v>6</v>
-      </c>
-      <c r="G62" t="n">
         <v>291</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="G62" s="1" t="n">
         <v>46026</v>
       </c>
-      <c r="I62" t="n">
+      <c r="H62" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>29</v>
-      </c>
-      <c r="B63" t="n">
         <v>30</v>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Rich</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Rich</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
           <t>+1 (558) 796-1667</t>
         </is>
       </c>
+      <c r="E63" t="n">
+        <v>7</v>
+      </c>
       <c r="F63" t="n">
-        <v>7</v>
-      </c>
-      <c r="G63" t="n">
         <v>13</v>
       </c>
-      <c r="H63" s="1" t="n">
+      <c r="G63" s="1" t="n">
         <v>46026</v>
       </c>
-      <c r="I63" t="n">
+      <c r="H63" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>180</v>
-      </c>
-      <c r="B64" t="n">
         <v>181</v>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
           <t>+1 (863) 508-5809</t>
         </is>
       </c>
+      <c r="E64" t="n">
+        <v>8</v>
+      </c>
       <c r="F64" t="n">
-        <v>8</v>
-      </c>
-      <c r="G64" t="n">
         <v>388</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="G64" s="1" t="n">
         <v>46027</v>
       </c>
-      <c r="I64" t="n">
+      <c r="H64" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>218</v>
-      </c>
-      <c r="B65" t="n">
         <v>219</v>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
           <t>+1 (755) 727-4831</t>
         </is>
       </c>
+      <c r="E65" t="n">
+        <v>16</v>
+      </c>
       <c r="F65" t="n">
-        <v>16</v>
-      </c>
-      <c r="G65" t="n">
         <v>397</v>
       </c>
-      <c r="H65" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46027</v>
       </c>
-      <c r="I65" t="n">
+      <c r="H65" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>85</v>
-      </c>
-      <c r="B66" t="n">
         <v>86</v>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
           <t>+1 (622) 790-2661</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="E66" t="n">
         <v>12</v>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" s="1" t="n">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" s="1" t="n">
         <v>46027</v>
       </c>
-      <c r="I66" t="n">
+      <c r="H66" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67</v>
-      </c>
-      <c r="B67" t="n">
         <v>68</v>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Conrad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Conrad</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
           <t>+1 (366) 851-8180</t>
         </is>
       </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
       <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
         <v>46</v>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="G67" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="I67" t="n">
+      <c r="H67" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>37</v>
-      </c>
-      <c r="B68" t="n">
         <v>38</v>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Butler</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
           <t>+1 (298) 796-3280</t>
         </is>
       </c>
+      <c r="E68" t="n">
+        <v>18</v>
+      </c>
       <c r="F68" t="n">
-        <v>18</v>
-      </c>
-      <c r="G68" t="n">
         <v>324</v>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="G68" s="1" t="n">
         <v>46029</v>
       </c>
-      <c r="I68" t="n">
+      <c r="H68" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>193</v>
-      </c>
-      <c r="B69" t="n">
         <v>194</v>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Barron</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Barron</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
           <t>+1 (362) 797-6530</t>
         </is>
       </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
       <c r="F69" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" t="n">
         <v>290</v>
       </c>
-      <c r="H69" s="1" t="n">
+      <c r="G69" s="1" t="n">
         <v>46029</v>
       </c>
-      <c r="I69" t="n">
+      <c r="H69" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>252</v>
-      </c>
-      <c r="B70" t="n">
         <v>253</v>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Anderson</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
           <t>+1 (723) 302-4673</t>
         </is>
       </c>
+      <c r="E70" t="n">
+        <v>9</v>
+      </c>
       <c r="F70" t="n">
-        <v>9</v>
-      </c>
-      <c r="G70" t="n">
         <v>268</v>
       </c>
-      <c r="H70" s="1" t="n">
+      <c r="G70" s="1" t="n">
         <v>46030</v>
       </c>
-      <c r="I70" t="n">
+      <c r="H70" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127</v>
-      </c>
-      <c r="B71" t="n">
         <v>128</v>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Randy</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Cox</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cox</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
           <t>+1 (544) 891-1682</t>
         </is>
       </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" t="n">
         <v>53</v>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="G71" s="1" t="n">
         <v>46030</v>
       </c>
-      <c r="I71" t="n">
+      <c r="H71" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>179</v>
-      </c>
-      <c r="B72" t="n">
         <v>180</v>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Carroll</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
           <t>+1 (384) 931-9908</t>
         </is>
       </c>
+      <c r="E72" t="n">
+        <v>9</v>
+      </c>
       <c r="F72" t="n">
-        <v>9</v>
-      </c>
-      <c r="G72" t="n">
         <v>224</v>
       </c>
-      <c r="H72" s="1" t="n">
+      <c r="G72" s="1" t="n">
         <v>46030</v>
       </c>
-      <c r="I72" t="n">
+      <c r="H72" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>48</v>
-      </c>
-      <c r="B73" t="n">
         <v>49</v>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Wilson</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
           <t>+1 (457) 569-4457</t>
         </is>
       </c>
+      <c r="E73" t="n">
+        <v>15</v>
+      </c>
       <c r="F73" t="n">
-        <v>15</v>
-      </c>
-      <c r="G73" t="n">
         <v>434</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="G73" s="1" t="n">
         <v>46030</v>
       </c>
-      <c r="I73" t="n">
+      <c r="H73" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>285</v>
-      </c>
-      <c r="B74" t="n">
         <v>286</v>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Mckinney</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mckinney</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
           <t>+1 (497) 218-5082</t>
         </is>
       </c>
+      <c r="E74" t="n">
+        <v>9</v>
+      </c>
       <c r="F74" t="n">
-        <v>9</v>
-      </c>
-      <c r="G74" t="n">
         <v>187</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="G74" s="1" t="n">
         <v>46031</v>
       </c>
-      <c r="I74" t="n">
+      <c r="H74" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>166</v>
-      </c>
-      <c r="B75" t="n">
         <v>167</v>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
           <t>+1 (701) 584-2737</t>
         </is>
       </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
       <c r="F75" t="n">
-        <v>13</v>
-      </c>
-      <c r="G75" t="n">
         <v>96</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="G75" s="1" t="n">
         <v>46031</v>
       </c>
-      <c r="I75" t="n">
+      <c r="H75" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>86</v>
-      </c>
-      <c r="B76" t="n">
         <v>87</v>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Johnson</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
           <t>+1 (309) 333-8775</t>
         </is>
       </c>
+      <c r="E76" t="n">
+        <v>11</v>
+      </c>
       <c r="F76" t="n">
-        <v>11</v>
-      </c>
-      <c r="G76" t="n">
         <v>228</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="G76" s="1" t="n">
         <v>46031</v>
       </c>
-      <c r="I76" t="n">
+      <c r="H76" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>156</v>
-      </c>
-      <c r="B77" t="n">
         <v>157</v>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Jeffery</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jeffery</t>
+          <t>Hoffman</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Hoffman</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
           <t>+1 (507) 483-2748</t>
         </is>
       </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
       <c r="F77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" t="n">
         <v>229</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="G77" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="I77" t="n">
+      <c r="H77" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>294</v>
-      </c>
-      <c r="B78" t="n">
         <v>295</v>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kelsey</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Carter</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
           <t>+1 (876) 351-3087</t>
         </is>
       </c>
+      <c r="E78" t="n">
+        <v>12</v>
+      </c>
       <c r="F78" t="n">
-        <v>12</v>
-      </c>
-      <c r="G78" t="n">
         <v>383</v>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="G78" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="I78" t="n">
+      <c r="H78" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>45</v>
-      </c>
-      <c r="B79" t="n">
         <v>46</v>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Shaun</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Shaun</t>
+          <t>Dorsey</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Dorsey</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
           <t>+1 (591) 793-5170</t>
         </is>
       </c>
+      <c r="E79" t="n">
+        <v>12</v>
+      </c>
       <c r="F79" t="n">
-        <v>12</v>
-      </c>
-      <c r="G79" t="n">
         <v>164</v>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="G79" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="I79" t="n">
+      <c r="H79" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>240</v>
-      </c>
-      <c r="B80" t="n">
         <v>241</v>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Frances</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Frances</t>
+          <t>Oneal</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Oneal</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
           <t>+1 (894) 704-8572</t>
         </is>
       </c>
+      <c r="E80" t="n">
+        <v>17</v>
+      </c>
       <c r="F80" t="n">
-        <v>17</v>
-      </c>
-      <c r="G80" t="n">
         <v>230</v>
       </c>
-      <c r="H80" s="1" t="n">
+      <c r="G80" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="I80" t="n">
+      <c r="H80" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>227</v>
-      </c>
-      <c r="B81" t="n">
         <v>228</v>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hall</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
           <t>+1 (887) 843-6153</t>
         </is>
       </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
       <c r="F81" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" t="n">
         <v>8</v>
       </c>
-      <c r="H81" s="1" t="n">
+      <c r="G81" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="I81" t="n">
+      <c r="H81" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>178</v>
-      </c>
-      <c r="B82" t="n">
         <v>179</v>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Russell</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
           <t>+1 (460) 903-8319</t>
         </is>
       </c>
+      <c r="E82" t="n">
+        <v>5</v>
+      </c>
       <c r="F82" t="n">
-        <v>5</v>
-      </c>
-      <c r="G82" t="n">
         <v>43</v>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="G82" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="I82" t="n">
+      <c r="H82" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>174</v>
-      </c>
-      <c r="B83" t="n">
         <v>175</v>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ross</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
           <t>+1 (588) 281-7834</t>
         </is>
       </c>
+      <c r="E83" t="n">
+        <v>3</v>
+      </c>
       <c r="F83" t="n">
-        <v>3</v>
-      </c>
-      <c r="G83" t="n">
         <v>182</v>
       </c>
-      <c r="H83" s="1" t="n">
+      <c r="G83" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="I83" t="n">
+      <c r="H83" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>197</v>
-      </c>
-      <c r="B84" t="n">
         <v>198</v>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Dawn</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Stanley</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
           <t>+1 (831) 223-8678</t>
         </is>
       </c>
+      <c r="E84" t="n">
+        <v>9</v>
+      </c>
       <c r="F84" t="n">
-        <v>9</v>
-      </c>
-      <c r="G84" t="n">
         <v>404</v>
       </c>
-      <c r="H84" s="1" t="n">
+      <c r="G84" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="I84" t="n">
+      <c r="H84" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>159</v>
-      </c>
-      <c r="B85" t="n">
         <v>160</v>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shannon</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Martinez</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
           <t>+1 (475) 825-4059</t>
         </is>
       </c>
+      <c r="E85" t="n">
+        <v>14</v>
+      </c>
       <c r="F85" t="n">
-        <v>14</v>
-      </c>
-      <c r="G85" t="n">
         <v>101</v>
       </c>
-      <c r="H85" s="1" t="n">
+      <c r="G85" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="I85" t="n">
+      <c r="H85" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>271</v>
-      </c>
-      <c r="B86" t="n">
         <v>272</v>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Gabrielle</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Lopez</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lopez</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
           <t>+1 (954) 566-3349</t>
         </is>
       </c>
+      <c r="E86" t="n">
+        <v>16</v>
+      </c>
       <c r="F86" t="n">
-        <v>16</v>
-      </c>
-      <c r="G86" t="n">
         <v>218</v>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="G86" s="1" t="n">
         <v>46034</v>
       </c>
-      <c r="I86" t="n">
+      <c r="H86" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>272</v>
-      </c>
-      <c r="B87" t="n">
         <v>273</v>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Johnson</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
           <t>+1 (952) 795-4056</t>
         </is>
       </c>
+      <c r="E87" t="n">
+        <v>11</v>
+      </c>
       <c r="F87" t="n">
-        <v>11</v>
-      </c>
-      <c r="G87" t="n">
         <v>173</v>
       </c>
-      <c r="H87" s="1" t="n">
+      <c r="G87" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="I87" t="n">
+      <c r="H87" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" t="n">
         <v>84</v>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Fields</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fields</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
           <t>+1 (782) 735-6541</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="E88" t="n">
         <v>8</v>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" s="1" t="n">
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" s="1" t="n">
         <v>46037</v>
       </c>
-      <c r="I88" t="n">
+      <c r="H88" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>150</v>
-      </c>
-      <c r="B89" t="n">
         <v>151</v>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Cline</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cline</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
           <t>+1 (500) 831-4555</t>
         </is>
       </c>
+      <c r="E89" t="n">
+        <v>17</v>
+      </c>
       <c r="F89" t="n">
-        <v>17</v>
-      </c>
-      <c r="G89" t="n">
         <v>461</v>
       </c>
-      <c r="H89" s="1" t="n">
+      <c r="G89" s="1" t="n">
         <v>46037</v>
       </c>
-      <c r="I89" t="n">
+      <c r="H89" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>11</v>
-      </c>
-      <c r="B90" t="n">
         <v>12</v>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Cox</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cox</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
           <t>+1 (548) 865-1283</t>
         </is>
       </c>
+      <c r="E90" t="n">
+        <v>10</v>
+      </c>
       <c r="F90" t="n">
-        <v>10</v>
-      </c>
-      <c r="G90" t="n">
         <v>275</v>
       </c>
-      <c r="H90" s="1" t="n">
+      <c r="G90" s="1" t="n">
         <v>46037</v>
       </c>
-      <c r="I90" t="n">
+      <c r="H90" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>232</v>
-      </c>
-      <c r="B91" t="n">
         <v>233</v>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Gilbert</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
           <t>+1 (351) 832-8800</t>
         </is>
       </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
       <c r="F91" t="n">
-        <v>5</v>
-      </c>
-      <c r="G91" t="n">
         <v>75</v>
       </c>
-      <c r="H91" s="1" t="n">
+      <c r="G91" s="1" t="n">
         <v>46037</v>
       </c>
-      <c r="I91" t="n">
+      <c r="H91" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>260</v>
-      </c>
-      <c r="B92" t="n">
         <v>261</v>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Moon</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
           <t>+1 (951) 736-6858</t>
         </is>
       </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
       <c r="F92" t="n">
-        <v>5</v>
-      </c>
-      <c r="G92" t="n">
         <v>480</v>
       </c>
-      <c r="H92" s="1" t="n">
+      <c r="G92" s="1" t="n">
         <v>46037</v>
       </c>
-      <c r="I92" t="n">
+      <c r="H92" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>291</v>
-      </c>
-      <c r="B93" t="n">
         <v>292</v>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Nixon</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Nixon</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
           <t>+1 (457) 827-4781</t>
         </is>
       </c>
+      <c r="E93" t="n">
+        <v>8</v>
+      </c>
       <c r="F93" t="n">
-        <v>8</v>
-      </c>
-      <c r="G93" t="n">
         <v>474</v>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="G93" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="I93" t="n">
+      <c r="H93" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>69</v>
-      </c>
-      <c r="B94" t="n">
         <v>70</v>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Derrick</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Liu</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
           <t>+1 (205) 707-5781</t>
         </is>
       </c>
+      <c r="E94" t="n">
+        <v>13</v>
+      </c>
       <c r="F94" t="n">
-        <v>13</v>
-      </c>
-      <c r="G94" t="n">
         <v>136</v>
       </c>
-      <c r="H94" s="1" t="n">
+      <c r="G94" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="I94" t="n">
+      <c r="H94" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>219</v>
-      </c>
-      <c r="B95" t="n">
         <v>220</v>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Rogers</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Rogers</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
           <t>+1 (531) 334-1767</t>
         </is>
       </c>
+      <c r="E95" t="n">
+        <v>15</v>
+      </c>
       <c r="F95" t="n">
-        <v>15</v>
-      </c>
-      <c r="G95" t="n">
         <v>171</v>
       </c>
-      <c r="H95" s="1" t="n">
+      <c r="G95" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="I95" t="n">
+      <c r="H95" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>13</v>
-      </c>
-      <c r="B96" t="n">
         <v>14</v>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Hinton</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Hinton</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
           <t>+1 (370) 599-1720</t>
         </is>
       </c>
+      <c r="E96" t="n">
+        <v>17</v>
+      </c>
       <c r="F96" t="n">
-        <v>17</v>
-      </c>
-      <c r="G96" t="n">
         <v>103</v>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="G96" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="I96" t="n">
+      <c r="H96" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>261</v>
-      </c>
-      <c r="B97" t="n">
         <v>262</v>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Sellers</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sellers</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
           <t>+1 (577) 843-1600</t>
         </is>
       </c>
+      <c r="E97" t="n">
+        <v>17</v>
+      </c>
       <c r="F97" t="n">
-        <v>17</v>
-      </c>
-      <c r="G97" t="n">
         <v>118</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="G97" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="I97" t="n">
+      <c r="H97" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129</v>
-      </c>
-      <c r="B98" t="n">
         <v>130</v>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Potter</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Potter</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
           <t>+1 (231) 491-1768</t>
         </is>
       </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
       <c r="F98" t="n">
-        <v>2</v>
-      </c>
-      <c r="G98" t="n">
         <v>76</v>
       </c>
-      <c r="H98" s="1" t="n">
+      <c r="G98" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="I98" t="n">
+      <c r="H98" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>113</v>
-      </c>
-      <c r="B99" t="n">
         <v>114</v>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Olsen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Olsen</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
           <t>+1 (484) 945-2335</t>
         </is>
       </c>
+      <c r="E99" t="n">
+        <v>7</v>
+      </c>
       <c r="F99" t="n">
-        <v>7</v>
-      </c>
-      <c r="G99" t="n">
         <v>361</v>
       </c>
-      <c r="H99" s="1" t="n">
+      <c r="G99" s="1" t="n">
         <v>46041</v>
       </c>
-      <c r="I99" t="n">
+      <c r="H99" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>287</v>
-      </c>
-      <c r="B100" t="n">
         <v>288</v>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
           <t>+1 (470) 427-1198</t>
         </is>
       </c>
+      <c r="E100" t="n">
+        <v>14</v>
+      </c>
       <c r="F100" t="n">
-        <v>14</v>
-      </c>
-      <c r="G100" t="n">
         <v>325</v>
       </c>
-      <c r="H100" s="1" t="n">
+      <c r="G100" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="I100" t="n">
+      <c r="H100" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>77</v>
-      </c>
-      <c r="B101" t="n">
         <v>78</v>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Mckenzie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mckenzie</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
           <t>+1 (597) 802-5752</t>
         </is>
       </c>
+      <c r="E101" t="n">
+        <v>6</v>
+      </c>
       <c r="F101" t="n">
-        <v>6</v>
-      </c>
-      <c r="G101" t="n">
         <v>264</v>
       </c>
-      <c r="H101" s="1" t="n">
+      <c r="G101" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="I101" t="n">
+      <c r="H101" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>34</v>
-      </c>
-      <c r="B102" t="n">
         <v>35</v>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Walsh</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Walsh</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
           <t>+1 (943) 746-6929</t>
         </is>
       </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
       <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
         <v>193</v>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="G102" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="I102" t="n">
+      <c r="H102" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>183</v>
-      </c>
-      <c r="B103" t="n">
         <v>184</v>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Bradley</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>Torres</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Torres</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
           <t>+1 (953) 872-9814</t>
         </is>
       </c>
+      <c r="E103" t="n">
+        <v>17</v>
+      </c>
       <c r="F103" t="n">
-        <v>17</v>
-      </c>
-      <c r="G103" t="n">
         <v>294</v>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="G103" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="I103" t="n">
+      <c r="H103" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>278</v>
-      </c>
-      <c r="B104" t="n">
         <v>279</v>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ellis</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
           <t>+1 (908) 271-1289</t>
         </is>
       </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
       <c r="F104" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" t="n">
         <v>399</v>
       </c>
-      <c r="H104" s="1" t="n">
+      <c r="G104" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="I104" t="n">
+      <c r="H104" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>283</v>
-      </c>
-      <c r="B105" t="n">
         <v>284</v>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Garcia</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
           <t>+1 (803) 556-5025</t>
         </is>
       </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
       <c r="F105" t="n">
-        <v>2</v>
-      </c>
-      <c r="G105" t="n">
         <v>122</v>
       </c>
-      <c r="H105" s="1" t="n">
+      <c r="G105" s="1" t="n">
         <v>46043</v>
       </c>
-      <c r="I105" t="n">
+      <c r="H105" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>251</v>
-      </c>
-      <c r="B106" t="n">
         <v>252</v>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Diaz</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Diaz</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
           <t>+1 (417) 312-6354</t>
         </is>
       </c>
+      <c r="E106" t="n">
+        <v>7</v>
+      </c>
       <c r="F106" t="n">
-        <v>7</v>
-      </c>
-      <c r="G106" t="n">
         <v>88</v>
       </c>
-      <c r="H106" s="1" t="n">
+      <c r="G106" s="1" t="n">
         <v>46043</v>
       </c>
-      <c r="I106" t="n">
+      <c r="H106" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>82</v>
-      </c>
-      <c r="B107" t="n">
         <v>83</v>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Mills</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mills</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
           <t>+1 (508) 266-9387</t>
         </is>
       </c>
+      <c r="E107" t="n">
+        <v>16</v>
+      </c>
       <c r="F107" t="n">
-        <v>16</v>
-      </c>
-      <c r="G107" t="n">
         <v>170</v>
       </c>
-      <c r="H107" s="1" t="n">
+      <c r="G107" s="1" t="n">
         <v>46044</v>
       </c>
-      <c r="I107" t="n">
+      <c r="H107" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>105</v>
-      </c>
-      <c r="B108" t="n">
         <v>106</v>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Philip</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Philip</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
           <t>+1 (829) 389-9197</t>
         </is>
       </c>
+      <c r="E108" t="n">
+        <v>3</v>
+      </c>
       <c r="F108" t="n">
-        <v>3</v>
-      </c>
-      <c r="G108" t="n">
         <v>248</v>
       </c>
-      <c r="H108" s="1" t="n">
+      <c r="G108" s="1" t="n">
         <v>46044</v>
       </c>
-      <c r="I108" t="n">
+      <c r="H108" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>177</v>
-      </c>
-      <c r="B109" t="n">
         <v>178</v>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Townsend</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
           <t>+1 (550) 825-2021</t>
         </is>
       </c>
+      <c r="E109" t="n">
+        <v>8</v>
+      </c>
       <c r="F109" t="n">
-        <v>8</v>
-      </c>
-      <c r="G109" t="n">
         <v>398</v>
       </c>
-      <c r="H109" s="1" t="n">
+      <c r="G109" s="1" t="n">
         <v>46044</v>
       </c>
-      <c r="I109" t="n">
+      <c r="H109" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>57</v>
-      </c>
-      <c r="B110" t="n">
         <v>58</v>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Travis</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Travis</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Daniels</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
           <t>+1 (813) 684-7649</t>
         </is>
       </c>
+      <c r="E110" t="n">
+        <v>7</v>
+      </c>
       <c r="F110" t="n">
-        <v>7</v>
-      </c>
-      <c r="G110" t="n">
         <v>411</v>
       </c>
-      <c r="H110" s="1" t="n">
+      <c r="G110" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="I110" t="n">
+      <c r="H110" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>212</v>
-      </c>
-      <c r="B111" t="n">
         <v>213</v>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
           <t>+1 (859) 867-4270</t>
         </is>
       </c>
+      <c r="E111" t="n">
+        <v>10</v>
+      </c>
       <c r="F111" t="n">
-        <v>10</v>
-      </c>
-      <c r="G111" t="n">
         <v>467</v>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="G111" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="I111" t="n">
+      <c r="H111" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>101</v>
-      </c>
-      <c r="B112" t="n">
         <v>102</v>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
           <t>+1 (271) 390-1317</t>
         </is>
       </c>
+      <c r="E112" t="n">
+        <v>10</v>
+      </c>
       <c r="F112" t="n">
-        <v>10</v>
-      </c>
-      <c r="G112" t="n">
         <v>110</v>
       </c>
-      <c r="H112" s="1" t="n">
+      <c r="G112" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="I112" t="n">
+      <c r="H112" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>170</v>
-      </c>
-      <c r="B113" t="n">
         <v>171</v>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Lara</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lara</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
           <t>+1 (578) 595-5420</t>
         </is>
       </c>
+      <c r="E113" t="n">
+        <v>10</v>
+      </c>
       <c r="F113" t="n">
-        <v>10</v>
-      </c>
-      <c r="G113" t="n">
         <v>183</v>
       </c>
-      <c r="H113" s="1" t="n">
+      <c r="G113" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="I113" t="n">
+      <c r="H113" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>229</v>
-      </c>
-      <c r="B114" t="n">
         <v>230</v>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Burns</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Burns</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
           <t>+1 (770) 928-9778</t>
         </is>
       </c>
+      <c r="E114" t="n">
+        <v>17</v>
+      </c>
       <c r="F114" t="n">
-        <v>17</v>
-      </c>
-      <c r="G114" t="n">
         <v>372</v>
       </c>
-      <c r="H114" s="1" t="n">
+      <c r="G114" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="I114" t="n">
+      <c r="H114" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>40</v>
-      </c>
-      <c r="B115" t="n">
         <v>41</v>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
           <t>+1 (586) 798-4028</t>
         </is>
       </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
       <c r="F115" t="n">
-        <v>4</v>
-      </c>
-      <c r="G115" t="n">
         <v>334</v>
       </c>
-      <c r="H115" s="1" t="n">
+      <c r="G115" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="I115" t="n">
+      <c r="H115" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>8</v>
-      </c>
-      <c r="B116" t="n">
         <v>9</v>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Christine</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
           <t>+1 (430) 534-7058</t>
         </is>
       </c>
+      <c r="E116" t="n">
+        <v>16</v>
+      </c>
       <c r="F116" t="n">
-        <v>16</v>
-      </c>
-      <c r="G116" t="n">
         <v>190</v>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="G116" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="I116" t="n">
+      <c r="H116" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>66</v>
-      </c>
-      <c r="B117" t="n">
         <v>67</v>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deborah</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Deborah</t>
+          <t>Pittman</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Pittman</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
           <t>+1 (249) 509-1261</t>
         </is>
       </c>
+      <c r="E117" t="n">
+        <v>12</v>
+      </c>
       <c r="F117" t="n">
-        <v>12</v>
-      </c>
-      <c r="G117" t="n">
         <v>429</v>
       </c>
-      <c r="H117" s="1" t="n">
+      <c r="G117" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="I117" t="n">
+      <c r="H117" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>51</v>
-      </c>
-      <c r="B118" t="n">
         <v>52</v>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Chavez</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Chavez</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
           <t>+1 (458) 255-4582</t>
         </is>
       </c>
+      <c r="E118" t="n">
+        <v>2</v>
+      </c>
       <c r="F118" t="n">
-        <v>2</v>
-      </c>
-      <c r="G118" t="n">
         <v>442</v>
       </c>
-      <c r="H118" s="1" t="n">
+      <c r="G118" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="I118" t="n">
+      <c r="H118" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>79</v>
-      </c>
-      <c r="B119" t="n">
         <v>80</v>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>Scott</t>
@@ -4565,794 +4216,723 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Scott</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
           <t>+1 (293) 633-7322</t>
         </is>
       </c>
+      <c r="E119" t="n">
+        <v>17</v>
+      </c>
       <c r="F119" t="n">
-        <v>17</v>
-      </c>
-      <c r="G119" t="n">
         <v>327</v>
       </c>
-      <c r="H119" s="1" t="n">
+      <c r="G119" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="I119" t="n">
+      <c r="H119" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>198</v>
-      </c>
-      <c r="B120" t="n">
         <v>199</v>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Jenkins</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
           <t>+1 (451) 449-1064</t>
         </is>
       </c>
+      <c r="E120" t="n">
+        <v>9</v>
+      </c>
       <c r="F120" t="n">
-        <v>9</v>
-      </c>
-      <c r="G120" t="n">
         <v>191</v>
       </c>
-      <c r="H120" s="1" t="n">
+      <c r="G120" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="I120" t="n">
+      <c r="H120" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>151</v>
-      </c>
-      <c r="B121" t="n">
         <v>152</v>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Porter</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Porter</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
           <t>+1 (332) 297-5019</t>
         </is>
       </c>
+      <c r="E121" t="n">
+        <v>8</v>
+      </c>
       <c r="F121" t="n">
-        <v>8</v>
-      </c>
-      <c r="G121" t="n">
         <v>119</v>
       </c>
-      <c r="H121" s="1" t="n">
+      <c r="G121" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="I121" t="n">
+      <c r="H121" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>255</v>
-      </c>
-      <c r="B122" t="n">
         <v>256</v>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Rachael</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rachael</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Scott</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
           <t>+1 (931) 628-7744</t>
         </is>
       </c>
+      <c r="E122" t="n">
+        <v>6</v>
+      </c>
       <c r="F122" t="n">
-        <v>6</v>
-      </c>
-      <c r="G122" t="n">
         <v>149</v>
       </c>
-      <c r="H122" s="1" t="n">
+      <c r="G122" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="I122" t="n">
+      <c r="H122" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>17</v>
-      </c>
-      <c r="B123" t="n">
         <v>18</v>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Lawrence</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lawrence</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
           <t>+1 (220) 418-7549</t>
         </is>
       </c>
+      <c r="E123" t="n">
+        <v>12</v>
+      </c>
       <c r="F123" t="n">
-        <v>12</v>
-      </c>
-      <c r="G123" t="n">
         <v>420</v>
       </c>
-      <c r="H123" s="1" t="n">
+      <c r="G123" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="I123" t="n">
+      <c r="H123" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>245</v>
-      </c>
-      <c r="B124" t="n">
         <v>246</v>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Jerry</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>Mccall</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mccall</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
           <t>+1 (979) 283-1833</t>
         </is>
       </c>
+      <c r="E124" t="n">
+        <v>13</v>
+      </c>
       <c r="F124" t="n">
-        <v>13</v>
-      </c>
-      <c r="G124" t="n">
         <v>80</v>
       </c>
-      <c r="H124" s="1" t="n">
+      <c r="G124" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="I124" t="n">
+      <c r="H124" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>96</v>
-      </c>
-      <c r="B125" t="n">
         <v>97</v>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Hector</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hector</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
           <t>+1 (501) 380-9928</t>
         </is>
       </c>
+      <c r="E125" t="n">
+        <v>12</v>
+      </c>
       <c r="F125" t="n">
-        <v>12</v>
-      </c>
-      <c r="G125" t="n">
         <v>344</v>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="G125" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="I125" t="n">
+      <c r="H125" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>205</v>
-      </c>
-      <c r="B126" t="n">
         <v>206</v>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Micheal</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Micheal</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ellis</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
           <t>+1 (271) 302-3364</t>
         </is>
       </c>
+      <c r="E126" t="n">
+        <v>12</v>
+      </c>
       <c r="F126" t="n">
-        <v>12</v>
-      </c>
-      <c r="G126" t="n">
         <v>459</v>
       </c>
-      <c r="H126" s="1" t="n">
+      <c r="G126" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="I126" t="n">
+      <c r="H126" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>233</v>
-      </c>
-      <c r="B127" t="n">
         <v>234</v>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ann</t>
+          <t>Caldwell</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Caldwell</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
           <t>+1 (815) 971-4915</t>
         </is>
       </c>
+      <c r="E127" t="n">
+        <v>18</v>
+      </c>
       <c r="F127" t="n">
-        <v>18</v>
-      </c>
-      <c r="G127" t="n">
         <v>414</v>
       </c>
-      <c r="H127" s="1" t="n">
+      <c r="G127" s="1" t="n">
         <v>46050</v>
       </c>
-      <c r="I127" t="n">
+      <c r="H127" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>221</v>
-      </c>
-      <c r="B128" t="n">
         <v>222</v>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tracy</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wilson</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
           <t>+1 (985) 331-5823</t>
         </is>
       </c>
+      <c r="E128" t="n">
+        <v>14</v>
+      </c>
       <c r="F128" t="n">
-        <v>14</v>
-      </c>
-      <c r="G128" t="n">
         <v>39</v>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="G128" s="1" t="n">
         <v>46050</v>
       </c>
-      <c r="I128" t="n">
+      <c r="H128" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>216</v>
-      </c>
-      <c r="B129" t="n">
         <v>217</v>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Jaclyn</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jaclyn</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Dean</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
           <t>+1 (611) 275-7057</t>
         </is>
       </c>
+      <c r="E129" t="n">
+        <v>13</v>
+      </c>
       <c r="F129" t="n">
-        <v>13</v>
-      </c>
-      <c r="G129" t="n">
         <v>219</v>
       </c>
-      <c r="H129" s="1" t="n">
+      <c r="G129" s="1" t="n">
         <v>46050</v>
       </c>
-      <c r="I129" t="n">
+      <c r="H129" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>38</v>
-      </c>
-      <c r="B130" t="n">
         <v>39</v>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Leah</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Leah</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
           <t>+1 (907) 923-6124</t>
         </is>
       </c>
+      <c r="E130" t="n">
+        <v>17</v>
+      </c>
       <c r="F130" t="n">
-        <v>17</v>
-      </c>
-      <c r="G130" t="n">
         <v>363</v>
       </c>
-      <c r="H130" s="1" t="n">
+      <c r="G130" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="I130" t="n">
+      <c r="H130" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>73</v>
-      </c>
-      <c r="B131" t="n">
         <v>74</v>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Knox</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Knox</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
           <t>+1 (804) 640-3507</t>
         </is>
       </c>
+      <c r="E131" t="n">
+        <v>11</v>
+      </c>
       <c r="F131" t="n">
-        <v>11</v>
-      </c>
-      <c r="G131" t="n">
         <v>231</v>
       </c>
-      <c r="H131" s="1" t="n">
+      <c r="G131" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="I131" t="n">
+      <c r="H131" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>213</v>
-      </c>
-      <c r="B132" t="n">
         <v>214</v>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Madison</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Mckenzie</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mckenzie</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
           <t>+1 (309) 349-3842</t>
         </is>
       </c>
+      <c r="E132" t="n">
+        <v>11</v>
+      </c>
       <c r="F132" t="n">
-        <v>11</v>
-      </c>
-      <c r="G132" t="n">
         <v>129</v>
       </c>
-      <c r="H132" s="1" t="n">
+      <c r="G132" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="I132" t="n">
+      <c r="H132" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>169</v>
-      </c>
-      <c r="B133" t="n">
         <v>170</v>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Jeffrey</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jeffrey</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Hernandez</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
           <t>+1 (291) 227-6701</t>
         </is>
       </c>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
       <c r="F133" t="n">
-        <v>4</v>
-      </c>
-      <c r="G133" t="n">
         <v>326</v>
       </c>
-      <c r="H133" s="1" t="n">
+      <c r="G133" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="I133" t="n">
+      <c r="H133" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>214</v>
-      </c>
-      <c r="B134" t="n">
         <v>215</v>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Kylie</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kylie</t>
+          <t>Gross</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Gross</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
           <t>+1 (216) 437-3588</t>
         </is>
       </c>
+      <c r="E134" t="n">
+        <v>11</v>
+      </c>
       <c r="F134" t="n">
-        <v>11</v>
-      </c>
-      <c r="G134" t="n">
         <v>155</v>
       </c>
-      <c r="H134" s="1" t="n">
+      <c r="G134" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="I134" t="n">
+      <c r="H134" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>187</v>
-      </c>
-      <c r="B135" t="n">
         <v>188</v>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Alvarado</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
           <t>+1 (208) 573-1909</t>
         </is>
       </c>
+      <c r="E135" t="n">
+        <v>11</v>
+      </c>
       <c r="F135" t="n">
-        <v>11</v>
-      </c>
-      <c r="G135" t="n">
         <v>176</v>
       </c>
-      <c r="H135" s="1" t="n">
+      <c r="G135" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="I135" t="n">
+      <c r="H135" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>7</v>
-      </c>
-      <c r="B136" t="n">
         <v>8</v>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Larsen</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Larsen</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
           <t>+1 (372) 479-5369</t>
         </is>
       </c>
+      <c r="E136" t="n">
+        <v>11</v>
+      </c>
       <c r="F136" t="n">
-        <v>11</v>
-      </c>
-      <c r="G136" t="n">
         <v>354</v>
       </c>
-      <c r="H136" s="1" t="n">
+      <c r="G136" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="I136" t="n">
+      <c r="H136" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>157</v>
-      </c>
-      <c r="B137" t="n">
         <v>158</v>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
           <t>+1 (481) 870-5978</t>
         </is>
       </c>
+      <c r="E137" t="n">
+        <v>16</v>
+      </c>
       <c r="F137" t="n">
-        <v>16</v>
-      </c>
-      <c r="G137" t="n">
         <v>445</v>
       </c>
-      <c r="H137" s="1" t="n">
+      <c r="G137" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="I137" t="n">
+      <c r="H137" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>206</v>
-      </c>
-      <c r="B138" t="n">
         <v>207</v>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Phillip</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Phillip</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Bryan</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
           <t>+1 (865) 665-9870</t>
         </is>
       </c>
+      <c r="E138" t="n">
+        <v>10</v>
+      </c>
       <c r="F138" t="n">
-        <v>10</v>
-      </c>
-      <c r="G138" t="n">
         <v>247</v>
       </c>
-      <c r="H138" s="1" t="n">
+      <c r="G138" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="I138" t="n">
+      <c r="H138" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>80</v>
-      </c>
-      <c r="B139" t="n">
         <v>81</v>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Christopher</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
           <t>+1 (210) 235-6938</t>
         </is>
       </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
       <c r="F139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" t="n">
         <v>69</v>
       </c>
-      <c r="H139" s="1" t="n">
+      <c r="G139" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="I139" t="n">
+      <c r="H139" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>249</v>
-      </c>
-      <c r="B140" t="n">
         <v>250</v>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Charles</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Garcia</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
           <t>+1 (841) 688-1827</t>
         </is>
       </c>
+      <c r="E140" t="n">
+        <v>12</v>
+      </c>
       <c r="F140" t="n">
-        <v>12</v>
-      </c>
-      <c r="G140" t="n">
         <v>217</v>
       </c>
-      <c r="H140" s="1" t="n">
+      <c r="G140" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="I140" t="n">
+      <c r="H140" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>84</v>
-      </c>
-      <c r="B141" t="n">
         <v>85</v>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Blackwell</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Blackwell</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
           <t>+1 (985) 916-7649</t>
         </is>
       </c>
+      <c r="E141" t="n">
+        <v>9</v>
+      </c>
       <c r="F141" t="n">
-        <v>9</v>
-      </c>
-      <c r="G141" t="n">
         <v>277</v>
       </c>
-      <c r="H141" s="1" t="n">
+      <c r="G141" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="I141" t="n">
+      <c r="H141" t="n">
         <v>10</v>
       </c>
     </row>
